--- a/src/main/resources/InternalContact_Field_Values.xlsx
+++ b/src/main/resources/InternalContact_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD56785-EA83-4CC4-820F-3C72DC42B7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB67DB9E-596C-4573-8F48-C40F6419ABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -90,40 +90,37 @@
     <t>Automation Runtime Contact</t>
   </si>
   <si>
-    <t>fieldMailingStreet</t>
-  </si>
-  <si>
-    <t>fieldMailingCity</t>
-  </si>
-  <si>
-    <t>fieldState__c</t>
-  </si>
-  <si>
-    <t>fieldMailingPostalCode</t>
-  </si>
-  <si>
-    <t>fieldMailingCountry</t>
-  </si>
-  <si>
     <t>VA</t>
   </si>
   <si>
-    <t>fieldPhone</t>
-  </si>
-  <si>
-    <t>fieldAccountId</t>
-  </si>
-  <si>
-    <t>fieldSalutation</t>
-  </si>
-  <si>
-    <t>fieldFirstName</t>
-  </si>
-  <si>
-    <t>fieldLastName</t>
-  </si>
-  <si>
-    <t>fieldEmail</t>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>AccountId</t>
+  </si>
+  <si>
+    <t>Salutation</t>
+  </si>
+  <si>
+    <t>MailingStreet</t>
+  </si>
+  <si>
+    <t>MailingCity</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>MailingPostalCode</t>
+  </si>
+  <si>
+    <t>MailingCountry</t>
   </si>
 </sst>
 </file>
@@ -462,14 +459,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.06640625" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.19921875" customWidth="1"/>
+    <col min="3" max="3" width="37.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,122 +477,122 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>20171</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -613,13 +610,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,7 +627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -641,7 +638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -652,7 +649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -675,14 +672,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>

--- a/src/main/resources/InternalContact_Field_Values.xlsx
+++ b/src/main/resources/InternalContact_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB67DB9E-596C-4573-8F48-C40F6419ABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55177E5E-5E6D-4F40-B6A6-99C2DD794A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -90,9 +90,6 @@
     <t>Automation Runtime Contact</t>
   </si>
   <si>
-    <t>VA</t>
-  </si>
-  <si>
     <t>FirstName</t>
   </si>
   <si>
@@ -121,13 +118,16 @@
   </si>
   <si>
     <t>MailingCountry</t>
+  </si>
+  <si>
+    <t>VA: Virginia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +142,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF211A1D"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -165,7 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -177,6 +183,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -459,14 +466,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.109375" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.21875" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,62 +484,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -543,56 +550,56 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
       </c>
       <c r="C11">
         <v>20171</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -610,13 +617,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6F275D-7657-4500-825C-5F565736E8FE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -627,7 +634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -638,7 +645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -649,7 +656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -672,14 +679,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F187A448-1415-4E32-A6B0-57F6ABB88CB8}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>

--- a/src/main/resources/InternalContact_Field_Values.xlsx
+++ b/src/main/resources/InternalContact_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB67DB9E-596C-4573-8F48-C40F6419ABFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B129B9B-3835-43F4-928E-2B53747AAC3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -90,9 +90,6 @@
     <t>Automation Runtime Contact</t>
   </si>
   <si>
-    <t>VA</t>
-  </si>
-  <si>
     <t>FirstName</t>
   </si>
   <si>
@@ -121,13 +118,16 @@
   </si>
   <si>
     <t>MailingCountry</t>
+  </si>
+  <si>
+    <t>VA: Virginia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +142,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -165,7 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -177,6 +183,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -482,7 +489,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -493,7 +500,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -504,7 +511,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -515,7 +522,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -526,7 +533,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
@@ -548,7 +555,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
@@ -559,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -570,10 +577,10 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -581,7 +588,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>20171</v>
@@ -592,7 +599,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
